--- a/artfynd/A 41277-2024 artfynd.xlsx
+++ b/artfynd/A 41277-2024 artfynd.xlsx
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121156589</v>
+        <v>121156646</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,26 +1203,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1230,10 +1234,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510642</v>
+        <v>510676</v>
       </c>
       <c r="R6" t="n">
-        <v>7002031</v>
+        <v>7002036</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1283,24 +1287,29 @@
           <t>Tallskog</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>På frisk och fuktig mark.</t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1318,10 +1327,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121095955</v>
+        <v>121096074</v>
       </c>
       <c r="B7" t="n">
-        <v>79680</v>
+        <v>56555</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1334,37 +1343,54 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510737</v>
+        <v>510762</v>
       </c>
       <c r="R7" t="n">
-        <v>7002020</v>
+        <v>7002010</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1405,7 +1431,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1432,7 +1457,7 @@
         <v>121096350</v>
       </c>
       <c r="B8" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1567,10 +1592,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121156657</v>
+        <v>121096097</v>
       </c>
       <c r="B9" t="n">
-        <v>78598</v>
+        <v>57504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1583,40 +1608,53 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Råkmyren, Jmt</t>
+          <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510671</v>
+        <v>510791</v>
       </c>
       <c r="R9" t="n">
-        <v>7001972</v>
+        <v>7001984</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1654,38 +1692,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Gles barrskog på frisk mark.</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1703,10 +1715,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121156646</v>
+        <v>121095955</v>
       </c>
       <c r="B10" t="n">
-        <v>79679</v>
+        <v>79683</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1719,44 +1731,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Råkmyren, Jmt</t>
+          <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510676</v>
+        <v>510737</v>
       </c>
       <c r="R10" t="n">
-        <v>7002036</v>
+        <v>7002020</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1800,32 +1808,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>På frisk och fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1843,10 +1826,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121095949</v>
+        <v>121156657</v>
       </c>
       <c r="B11" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1859,21 +1842,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1882,17 +1865,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stugumyren, Stugumyren, Jmt</t>
+          <t>Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510737</v>
+        <v>510671</v>
       </c>
       <c r="R11" t="n">
-        <v>7002019</v>
+        <v>7001972</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1937,6 +1920,31 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Gles barrskog på frisk mark.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1954,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121096097</v>
+        <v>121095949</v>
       </c>
       <c r="B12" t="n">
-        <v>57501</v>
+        <v>79682</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1970,50 +1978,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510791</v>
+        <v>510737</v>
       </c>
       <c r="R12" t="n">
-        <v>7001984</v>
+        <v>7002019</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2054,6 +2049,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2077,10 +2073,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121096074</v>
+        <v>121156589</v>
       </c>
       <c r="B13" t="n">
-        <v>56552</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2093,57 +2089,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stugumyren, Stugumyren, Jmt</t>
+          <t>Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510762</v>
+        <v>510642</v>
       </c>
       <c r="R13" t="n">
-        <v>7002010</v>
+        <v>7002031</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2181,12 +2160,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 41277-2024 artfynd.xlsx
+++ b/artfynd/A 41277-2024 artfynd.xlsx
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121156646</v>
+        <v>121156589</v>
       </c>
       <c r="B6" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,30 +1203,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1234,10 +1230,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510676</v>
+        <v>510642</v>
       </c>
       <c r="R6" t="n">
-        <v>7002036</v>
+        <v>7002031</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1287,29 +1283,24 @@
           <t>Tallskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>På frisk och fuktig mark.</t>
-        </is>
-      </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1327,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121096074</v>
+        <v>121095949</v>
       </c>
       <c r="B7" t="n">
-        <v>56555</v>
+        <v>79682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1343,54 +1334,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510762</v>
+        <v>510737</v>
       </c>
       <c r="R7" t="n">
-        <v>7002010</v>
+        <v>7002019</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1431,6 +1405,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1454,10 +1429,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121096350</v>
+        <v>121096097</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>57504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1466,43 +1441,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1510,14 +1481,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Råkmyren, Råkmyren, Jmt</t>
+          <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510665</v>
+        <v>510791</v>
       </c>
       <c r="R8" t="n">
-        <v>7001966</v>
+        <v>7001984</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1552,29 +1523,18 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 40 st skott/stjälkar och 1 st. fröställning av knärot.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Gles barrskog på frisk mark.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1592,10 +1552,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121096097</v>
+        <v>121096074</v>
       </c>
       <c r="B9" t="n">
-        <v>57504</v>
+        <v>56555</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1608,21 +1568,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1630,7 +1590,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
@@ -1648,10 +1612,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510791</v>
+        <v>510762</v>
       </c>
       <c r="R9" t="n">
-        <v>7001984</v>
+        <v>7002010</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1826,10 +1790,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121156657</v>
+        <v>121156646</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1842,26 +1806,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1869,10 +1837,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510671</v>
+        <v>510676</v>
       </c>
       <c r="R11" t="n">
-        <v>7001972</v>
+        <v>7002036</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1919,32 +1887,32 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Gles barrskog på frisk mark.</t>
+          <t>På frisk och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1962,10 +1930,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121095949</v>
+        <v>121096350</v>
       </c>
       <c r="B12" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1974,41 +1942,58 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stugumyren, Stugumyren, Jmt</t>
+          <t>Råkmyren, Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510737</v>
+        <v>510665</v>
       </c>
       <c r="R12" t="n">
-        <v>7002019</v>
+        <v>7001966</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2043,6 +2028,11 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 40 st skott/stjälkar och 1 st. fröställning av knärot.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2056,6 +2046,11 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gles barrskog på frisk mark.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2073,7 +2068,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121156589</v>
+        <v>121156657</v>
       </c>
       <c r="B13" t="n">
         <v>78601</v>
@@ -2116,10 +2111,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510642</v>
+        <v>510671</v>
       </c>
       <c r="R13" t="n">
-        <v>7002031</v>
+        <v>7001972</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2166,7 +2161,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gles barrskog på frisk mark.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">

--- a/artfynd/A 41277-2024 artfynd.xlsx
+++ b/artfynd/A 41277-2024 artfynd.xlsx
@@ -1190,7 +1190,7 @@
         <v>121156589</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121095949</v>
+        <v>121095955</v>
       </c>
       <c r="B7" t="n">
-        <v>79682</v>
+        <v>79686</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1334,21 +1334,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1364,7 +1364,7 @@
         <v>510737</v>
       </c>
       <c r="R7" t="n">
-        <v>7002019</v>
+        <v>7002020</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121096097</v>
+        <v>121156646</v>
       </c>
       <c r="B8" t="n">
-        <v>57504</v>
+        <v>79685</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1445,53 +1445,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stugumyren, Stugumyren, Jmt</t>
+          <t>Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510791</v>
+        <v>510676</v>
       </c>
       <c r="R8" t="n">
-        <v>7001984</v>
+        <v>7002036</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1529,12 +1520,38 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>På frisk och fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1552,10 +1569,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121096074</v>
+        <v>121095949</v>
       </c>
       <c r="B9" t="n">
-        <v>56555</v>
+        <v>79685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1568,54 +1585,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510762</v>
+        <v>510737</v>
       </c>
       <c r="R9" t="n">
-        <v>7002010</v>
+        <v>7002019</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1656,6 +1656,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1679,10 +1680,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121095955</v>
+        <v>121096097</v>
       </c>
       <c r="B10" t="n">
-        <v>79683</v>
+        <v>57504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1695,37 +1696,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510737</v>
+        <v>510791</v>
       </c>
       <c r="R10" t="n">
-        <v>7002020</v>
+        <v>7001984</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1766,7 +1780,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1790,10 +1803,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121156646</v>
+        <v>121096350</v>
       </c>
       <c r="B11" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1802,48 +1815,61 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Råkmyren, Jmt</t>
+          <t>Råkmyren, Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510676</v>
+        <v>510665</v>
       </c>
       <c r="R11" t="n">
-        <v>7002036</v>
+        <v>7001966</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1873,6 +1899,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 40 st skott/stjälkar och 1 st. fröställning av knärot.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,32 +1918,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>På frisk och fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Gles barrskog på frisk mark.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1930,10 +1941,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121096350</v>
+        <v>121156657</v>
       </c>
       <c r="B12" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1942,61 +1953,44 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Råkmyren, Råkmyren, Jmt</t>
+          <t>Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510665</v>
+        <v>510671</v>
       </c>
       <c r="R12" t="n">
-        <v>7001966</v>
+        <v>7001972</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2026,11 +2020,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 40 st skott/stjälkar och 1 st. fröställning av knärot.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2051,6 +2040,26 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>Gles barrskog på frisk mark.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2068,10 +2077,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121156657</v>
+        <v>121096074</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>56555</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2084,40 +2093,57 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Råkmyren, Jmt</t>
+          <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510671</v>
+        <v>510762</v>
       </c>
       <c r="R13" t="n">
-        <v>7001972</v>
+        <v>7002010</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2155,38 +2181,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Gles barrskog på frisk mark.</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 41277-2024 artfynd.xlsx
+++ b/artfynd/A 41277-2024 artfynd.xlsx
@@ -1187,7 +1187,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121156589</v>
+        <v>121156657</v>
       </c>
       <c r="B6" t="n">
         <v>78604</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510642</v>
+        <v>510671</v>
       </c>
       <c r="R6" t="n">
-        <v>7002031</v>
+        <v>7001972</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1280,7 +1280,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gles barrskog på frisk mark.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1318,10 +1323,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121095955</v>
+        <v>121096097</v>
       </c>
       <c r="B7" t="n">
-        <v>79686</v>
+        <v>57504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1334,37 +1339,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510737</v>
+        <v>510791</v>
       </c>
       <c r="R7" t="n">
-        <v>7002020</v>
+        <v>7001984</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1405,7 +1423,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1429,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121156646</v>
+        <v>121096350</v>
       </c>
       <c r="B8" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1441,48 +1458,61 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Råkmyren, Jmt</t>
+          <t>Råkmyren, Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510676</v>
+        <v>510665</v>
       </c>
       <c r="R8" t="n">
-        <v>7002036</v>
+        <v>7001966</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1512,6 +1542,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 40 st skott/stjälkar och 1 st. fröställning av knärot.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,32 +1561,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>På frisk och fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Gles barrskog på frisk mark.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1569,10 +1584,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121095949</v>
+        <v>121096074</v>
       </c>
       <c r="B9" t="n">
-        <v>79685</v>
+        <v>56555</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1585,37 +1600,54 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510737</v>
+        <v>510762</v>
       </c>
       <c r="R9" t="n">
-        <v>7002019</v>
+        <v>7002010</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1656,7 +1688,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1680,10 +1711,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121096097</v>
+        <v>121095955</v>
       </c>
       <c r="B10" t="n">
-        <v>57504</v>
+        <v>79686</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1696,50 +1727,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510791</v>
+        <v>510737</v>
       </c>
       <c r="R10" t="n">
-        <v>7001984</v>
+        <v>7002020</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1780,6 +1798,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1803,10 +1822,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121096350</v>
+        <v>121156589</v>
       </c>
       <c r="B11" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1815,61 +1834,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Råkmyren, Råkmyren, Jmt</t>
+          <t>Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510665</v>
+        <v>510642</v>
       </c>
       <c r="R11" t="n">
-        <v>7001966</v>
+        <v>7002031</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1899,11 +1901,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 40 st skott/stjälkar och 1 st. fröställning av knärot.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1918,12 +1915,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Gles barrskog på frisk mark.</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1941,10 +1953,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121156657</v>
+        <v>121095949</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1957,21 +1969,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1980,17 +1992,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Råkmyren, Jmt</t>
+          <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510671</v>
+        <v>510737</v>
       </c>
       <c r="R12" t="n">
-        <v>7001972</v>
+        <v>7002019</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2035,31 +2047,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gles barrskog på frisk mark.</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2077,10 +2064,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121096074</v>
+        <v>121156646</v>
       </c>
       <c r="B13" t="n">
-        <v>56555</v>
+        <v>79685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2093,57 +2080,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stugumyren, Stugumyren, Jmt</t>
+          <t>Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510762</v>
+        <v>510676</v>
       </c>
       <c r="R13" t="n">
-        <v>7002010</v>
+        <v>7002036</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2181,12 +2155,38 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>På frisk och fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 41277-2024 artfynd.xlsx
+++ b/artfynd/A 41277-2024 artfynd.xlsx
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121156657</v>
+        <v>121096074</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>56558</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,40 +1203,57 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råkmyren, Jmt</t>
+          <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510671</v>
+        <v>510762</v>
       </c>
       <c r="R6" t="n">
-        <v>7001972</v>
+        <v>7002010</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1274,38 +1291,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gles barrskog på frisk mark.</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1323,10 +1314,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121096097</v>
+        <v>121156646</v>
       </c>
       <c r="B7" t="n">
-        <v>57504</v>
+        <v>79688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1339,53 +1330,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stugumyren, Stugumyren, Jmt</t>
+          <t>Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510791</v>
+        <v>510676</v>
       </c>
       <c r="R7" t="n">
-        <v>7001984</v>
+        <v>7002036</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1423,12 +1405,38 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>På frisk och fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1446,10 +1454,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121096350</v>
+        <v>121095949</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1458,58 +1466,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Råkmyren, Råkmyren, Jmt</t>
+          <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510665</v>
+        <v>510737</v>
       </c>
       <c r="R8" t="n">
-        <v>7001966</v>
+        <v>7002019</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,11 +1535,6 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 40 st skott/stjälkar och 1 st. fröställning av knärot.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1562,11 +1548,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Gles barrskog på frisk mark.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1584,10 +1565,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121096074</v>
+        <v>121095955</v>
       </c>
       <c r="B9" t="n">
-        <v>56555</v>
+        <v>79689</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1600,54 +1581,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510762</v>
+        <v>510737</v>
       </c>
       <c r="R9" t="n">
-        <v>7002010</v>
+        <v>7002020</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1688,6 +1652,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1711,10 +1676,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121095955</v>
+        <v>121156589</v>
       </c>
       <c r="B10" t="n">
-        <v>79686</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1727,21 +1692,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1750,17 +1715,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stugumyren, Stugumyren, Jmt</t>
+          <t>Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510737</v>
+        <v>510642</v>
       </c>
       <c r="R10" t="n">
-        <v>7002020</v>
+        <v>7002031</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1804,7 +1769,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1822,10 +1807,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121156589</v>
+        <v>121096350</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1834,44 +1819,61 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Råkmyren, Jmt</t>
+          <t>Råkmyren, Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510642</v>
+        <v>510665</v>
       </c>
       <c r="R11" t="n">
-        <v>7002031</v>
+        <v>7001966</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1901,6 +1903,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 40 st skott/stjälkar och 1 st. fröställning av knärot.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1915,27 +1922,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Gles barrskog på frisk mark.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1953,10 +1945,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121095949</v>
+        <v>121156657</v>
       </c>
       <c r="B12" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1969,21 +1961,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1992,17 +1984,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stugumyren, Stugumyren, Jmt</t>
+          <t>Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510737</v>
+        <v>510671</v>
       </c>
       <c r="R12" t="n">
-        <v>7002019</v>
+        <v>7001972</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2047,6 +2039,31 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gles barrskog på frisk mark.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2064,10 +2081,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121156646</v>
+        <v>121096097</v>
       </c>
       <c r="B13" t="n">
-        <v>79685</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2080,44 +2097,53 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Råkmyren, Jmt</t>
+          <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510676</v>
+        <v>510791</v>
       </c>
       <c r="R13" t="n">
-        <v>7002036</v>
+        <v>7001984</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2155,38 +2181,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>På frisk och fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 41277-2024 artfynd.xlsx
+++ b/artfynd/A 41277-2024 artfynd.xlsx
@@ -1187,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121096074</v>
+        <v>121095955</v>
       </c>
       <c r="B6" t="n">
-        <v>56558</v>
+        <v>79689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,54 +1203,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510762</v>
+        <v>510737</v>
       </c>
       <c r="R6" t="n">
-        <v>7002010</v>
+        <v>7002020</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1291,6 +1274,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1314,7 +1298,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121156646</v>
+        <v>121095949</v>
       </c>
       <c r="B7" t="n">
         <v>79688</v>
@@ -1349,25 +1333,21 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Råkmyren, Jmt</t>
+          <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510676</v>
+        <v>510737</v>
       </c>
       <c r="R7" t="n">
-        <v>7002036</v>
+        <v>7002019</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1411,32 +1391,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>På frisk och fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1454,10 +1409,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121095949</v>
+        <v>121096097</v>
       </c>
       <c r="B8" t="n">
-        <v>79688</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1470,37 +1425,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510737</v>
+        <v>510791</v>
       </c>
       <c r="R8" t="n">
-        <v>7002019</v>
+        <v>7001984</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1541,7 +1509,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1565,10 +1532,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121095955</v>
+        <v>121096074</v>
       </c>
       <c r="B9" t="n">
-        <v>79689</v>
+        <v>56558</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1581,37 +1548,54 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stugumyren, Stugumyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510737</v>
+        <v>510762</v>
       </c>
       <c r="R9" t="n">
-        <v>7002020</v>
+        <v>7002010</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1652,7 +1636,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1676,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121156589</v>
+        <v>121156646</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1692,26 +1675,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1719,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510642</v>
+        <v>510676</v>
       </c>
       <c r="R10" t="n">
-        <v>7002031</v>
+        <v>7002036</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1772,24 +1759,29 @@
           <t>Tallskog</t>
         </is>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>På frisk och fuktig mark.</t>
+        </is>
+      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2081,10 +2073,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121096097</v>
+        <v>121156589</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2097,53 +2089,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stugumyren, Stugumyren, Jmt</t>
+          <t>Råkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510791</v>
+        <v>510642</v>
       </c>
       <c r="R13" t="n">
-        <v>7001984</v>
+        <v>7002031</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2181,12 +2160,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
